--- a/algorithm/output_result/return_metrics/HDFC_nav_Return_Metrics.xlsx
+++ b/algorithm/output_result/return_metrics/HDFC_nav_Return_Metrics.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G21"/>
+  <dimension ref="A1:L21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -452,6 +452,31 @@
           <t>1Y Return (%)</t>
         </is>
       </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Average Return</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>Broad Category</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>Return Rank</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>Funds in Category</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>Return Score</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -481,6 +506,23 @@
       <c r="G2" t="n">
         <v>3.65</v>
       </c>
+      <c r="H2" t="n">
+        <v>4.955</v>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Equity</t>
+        </is>
+      </c>
+      <c r="J2" t="n">
+        <v>3</v>
+      </c>
+      <c r="K2" t="n">
+        <v>14</v>
+      </c>
+      <c r="L2" t="n">
+        <v>84.62</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -510,6 +552,23 @@
       <c r="G3" t="n">
         <v>0.13</v>
       </c>
+      <c r="H3" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Equity</t>
+        </is>
+      </c>
+      <c r="J3" t="n">
+        <v>10</v>
+      </c>
+      <c r="K3" t="n">
+        <v>14</v>
+      </c>
+      <c r="L3" t="n">
+        <v>30.77</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -539,6 +598,23 @@
       <c r="G4" t="n">
         <v>5.68</v>
       </c>
+      <c r="H4" t="n">
+        <v>2.565</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Debt</t>
+        </is>
+      </c>
+      <c r="J4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K4" t="n">
+        <v>3</v>
+      </c>
+      <c r="L4" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -568,6 +644,23 @@
       <c r="G5" t="n">
         <v>-3.04</v>
       </c>
+      <c r="H5" t="n">
+        <v>-2.055</v>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Equity</t>
+        </is>
+      </c>
+      <c r="J5" t="n">
+        <v>14</v>
+      </c>
+      <c r="K5" t="n">
+        <v>14</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -597,6 +690,23 @@
       <c r="G6" t="n">
         <v>1.24</v>
       </c>
+      <c r="H6" t="n">
+        <v>0.9875</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Hybrid</t>
+        </is>
+      </c>
+      <c r="J6" t="n">
+        <v>2</v>
+      </c>
+      <c r="K6" t="n">
+        <v>3</v>
+      </c>
+      <c r="L6" t="n">
+        <v>50</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -626,6 +736,23 @@
       <c r="G7" t="n">
         <v>-1.68</v>
       </c>
+      <c r="H7" t="n">
+        <v>-1.385</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Equity</t>
+        </is>
+      </c>
+      <c r="J7" t="n">
+        <v>13</v>
+      </c>
+      <c r="K7" t="n">
+        <v>14</v>
+      </c>
+      <c r="L7" t="n">
+        <v>7.69</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -655,6 +782,23 @@
       <c r="G8" t="n">
         <v>2.33</v>
       </c>
+      <c r="H8" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Debt</t>
+        </is>
+      </c>
+      <c r="J8" t="n">
+        <v>3</v>
+      </c>
+      <c r="K8" t="n">
+        <v>3</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -684,6 +828,23 @@
       <c r="G9" t="n">
         <v>7.59</v>
       </c>
+      <c r="H9" t="n">
+        <v>5.6375</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Equity</t>
+        </is>
+      </c>
+      <c r="J9" t="n">
+        <v>1</v>
+      </c>
+      <c r="K9" t="n">
+        <v>14</v>
+      </c>
+      <c r="L9" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -713,6 +874,23 @@
       <c r="G10" t="n">
         <v>-1.22</v>
       </c>
+      <c r="H10" t="n">
+        <v>-0.725</v>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Equity</t>
+        </is>
+      </c>
+      <c r="J10" t="n">
+        <v>12</v>
+      </c>
+      <c r="K10" t="n">
+        <v>14</v>
+      </c>
+      <c r="L10" t="n">
+        <v>15.38</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -742,6 +920,23 @@
       <c r="G11" t="n">
         <v>3.77</v>
       </c>
+      <c r="H11" t="n">
+        <v>2.225</v>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Debt</t>
+        </is>
+      </c>
+      <c r="J11" t="n">
+        <v>2</v>
+      </c>
+      <c r="K11" t="n">
+        <v>3</v>
+      </c>
+      <c r="L11" t="n">
+        <v>50</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -771,6 +966,23 @@
       <c r="G12" t="n">
         <v>2.84</v>
       </c>
+      <c r="H12" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Hybrid</t>
+        </is>
+      </c>
+      <c r="J12" t="n">
+        <v>1</v>
+      </c>
+      <c r="K12" t="n">
+        <v>3</v>
+      </c>
+      <c r="L12" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -800,6 +1012,23 @@
       <c r="G13" t="n">
         <v>-0.26</v>
       </c>
+      <c r="H13" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Equity</t>
+        </is>
+      </c>
+      <c r="J13" t="n">
+        <v>9</v>
+      </c>
+      <c r="K13" t="n">
+        <v>14</v>
+      </c>
+      <c r="L13" t="n">
+        <v>38.46</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -829,6 +1058,23 @@
       <c r="G14" t="n">
         <v>-1.49</v>
       </c>
+      <c r="H14" t="n">
+        <v>0.385</v>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Equity</t>
+        </is>
+      </c>
+      <c r="J14" t="n">
+        <v>7</v>
+      </c>
+      <c r="K14" t="n">
+        <v>14</v>
+      </c>
+      <c r="L14" t="n">
+        <v>53.85</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -858,6 +1104,23 @@
       <c r="G15" t="n">
         <v>2.97</v>
       </c>
+      <c r="H15" t="n">
+        <v>3.6225</v>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>Equity</t>
+        </is>
+      </c>
+      <c r="J15" t="n">
+        <v>4</v>
+      </c>
+      <c r="K15" t="n">
+        <v>14</v>
+      </c>
+      <c r="L15" t="n">
+        <v>76.92</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -887,6 +1150,23 @@
       <c r="G16" t="n">
         <v>-3.65</v>
       </c>
+      <c r="H16" t="n">
+        <v>0.3350000000000001</v>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Equity</t>
+        </is>
+      </c>
+      <c r="J16" t="n">
+        <v>8</v>
+      </c>
+      <c r="K16" t="n">
+        <v>14</v>
+      </c>
+      <c r="L16" t="n">
+        <v>46.15</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -916,6 +1196,23 @@
       <c r="G17" t="n">
         <v>1.78</v>
       </c>
+      <c r="H17" t="n">
+        <v>5.065</v>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>Equity</t>
+        </is>
+      </c>
+      <c r="J17" t="n">
+        <v>2</v>
+      </c>
+      <c r="K17" t="n">
+        <v>14</v>
+      </c>
+      <c r="L17" t="n">
+        <v>92.31</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -945,6 +1242,23 @@
       <c r="G18" t="n">
         <v>-1.67</v>
       </c>
+      <c r="H18" t="n">
+        <v>-0.875</v>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>Hybrid</t>
+        </is>
+      </c>
+      <c r="J18" t="n">
+        <v>3</v>
+      </c>
+      <c r="K18" t="n">
+        <v>3</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -972,6 +1286,23 @@
         <v>0.84</v>
       </c>
       <c r="G19" t="inlineStr"/>
+      <c r="H19" t="n">
+        <v>-0.22</v>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>Equity</t>
+        </is>
+      </c>
+      <c r="J19" t="n">
+        <v>11</v>
+      </c>
+      <c r="K19" t="n">
+        <v>14</v>
+      </c>
+      <c r="L19" t="n">
+        <v>23.08</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -999,6 +1330,23 @@
         <v>-0.17</v>
       </c>
       <c r="G20" t="inlineStr"/>
+      <c r="H20" t="n">
+        <v>1.106666666666667</v>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>Equity</t>
+        </is>
+      </c>
+      <c r="J20" t="n">
+        <v>6</v>
+      </c>
+      <c r="K20" t="n">
+        <v>14</v>
+      </c>
+      <c r="L20" t="n">
+        <v>61.54</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1024,6 +1372,23 @@
       </c>
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr"/>
+      <c r="H21" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>Equity</t>
+        </is>
+      </c>
+      <c r="J21" t="n">
+        <v>5</v>
+      </c>
+      <c r="K21" t="n">
+        <v>14</v>
+      </c>
+      <c r="L21" t="n">
+        <v>69.23</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/algorithm/output_result/return_metrics/HDFC_nav_Return_Metrics.xlsx
+++ b/algorithm/output_result/return_metrics/HDFC_nav_Return_Metrics.xlsx
@@ -495,19 +495,19 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>1.88</v>
+        <v>2.69</v>
       </c>
       <c r="E2" t="n">
-        <v>5.06</v>
+        <v>5.96</v>
       </c>
       <c r="F2" t="n">
-        <v>9.23</v>
+        <v>6.96</v>
       </c>
       <c r="G2" t="n">
-        <v>3.65</v>
+        <v>6.08</v>
       </c>
       <c r="H2" t="n">
-        <v>4.955</v>
+        <v>5.422499999999999</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -515,13 +515,13 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K2" t="n">
         <v>14</v>
       </c>
       <c r="L2" t="n">
-        <v>84.62</v>
+        <v>92.31</v>
       </c>
     </row>
     <row r="3">
@@ -541,19 +541,19 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>1.5</v>
+        <v>4.76</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.45</v>
+        <v>5.29</v>
       </c>
       <c r="F3" t="n">
-        <v>-1.98</v>
+        <v>-0.28</v>
       </c>
       <c r="G3" t="n">
-        <v>0.13</v>
+        <v>3.06</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.2</v>
+        <v>3.2075</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -561,13 +561,13 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="K3" t="n">
         <v>14</v>
       </c>
       <c r="L3" t="n">
-        <v>30.77</v>
+        <v>53.85</v>
       </c>
     </row>
     <row r="4">
@@ -587,19 +587,19 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.44</v>
+        <v>0.47</v>
       </c>
       <c r="E4" t="n">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="F4" t="n">
-        <v>2.77</v>
+        <v>2.79</v>
       </c>
       <c r="G4" t="n">
-        <v>5.68</v>
+        <v>5.67</v>
       </c>
       <c r="H4" t="n">
-        <v>2.565</v>
+        <v>2.58</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -633,19 +633,19 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.09</v>
+        <v>2.1</v>
       </c>
       <c r="E5" t="n">
-        <v>-1.76</v>
+        <v>1.52</v>
       </c>
       <c r="F5" t="n">
-        <v>-3.51</v>
+        <v>-3.6</v>
       </c>
       <c r="G5" t="n">
-        <v>-3.04</v>
+        <v>-0.74</v>
       </c>
       <c r="H5" t="n">
-        <v>-2.055</v>
+        <v>-0.18</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -679,19 +679,19 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.79</v>
+        <v>1.4</v>
       </c>
       <c r="E6" t="n">
-        <v>1.2</v>
+        <v>3.62</v>
       </c>
       <c r="F6" t="n">
-        <v>0.72</v>
+        <v>0.42</v>
       </c>
       <c r="G6" t="n">
-        <v>1.24</v>
+        <v>2.79</v>
       </c>
       <c r="H6" t="n">
-        <v>0.9875</v>
+        <v>2.0575</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -699,13 +699,13 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K6" t="n">
         <v>3</v>
       </c>
       <c r="L6" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
     </row>
     <row r="7">
@@ -725,19 +725,19 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.13</v>
+        <v>2.25</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.35</v>
+        <v>1.94</v>
       </c>
       <c r="F7" t="n">
-        <v>-2.64</v>
+        <v>-2.72</v>
       </c>
       <c r="G7" t="n">
-        <v>-1.68</v>
+        <v>0.82</v>
       </c>
       <c r="H7" t="n">
-        <v>-1.385</v>
+        <v>0.5724999999999998</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -771,19 +771,19 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.62</v>
+        <v>-0.3</v>
       </c>
       <c r="E8" t="n">
-        <v>1.86</v>
+        <v>2.35</v>
       </c>
       <c r="F8" t="n">
-        <v>2.47</v>
+        <v>2.21</v>
       </c>
       <c r="G8" t="n">
-        <v>2.33</v>
+        <v>2.63</v>
       </c>
       <c r="H8" t="n">
-        <v>1.82</v>
+        <v>1.7225</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -817,19 +817,19 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0.49</v>
+        <v>1.92</v>
       </c>
       <c r="E9" t="n">
-        <v>4.21</v>
+        <v>5.39</v>
       </c>
       <c r="F9" t="n">
-        <v>10.26</v>
+        <v>8.279999999999999</v>
       </c>
       <c r="G9" t="n">
-        <v>7.59</v>
+        <v>9.960000000000001</v>
       </c>
       <c r="H9" t="n">
-        <v>5.6375</v>
+        <v>6.3875</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -863,19 +863,19 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.19</v>
+        <v>2.07</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.88</v>
+        <v>2.15</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.99</v>
+        <v>-1.4</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.22</v>
+        <v>1.21</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.725</v>
+        <v>1.0075</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -883,13 +883,13 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="K10" t="n">
         <v>14</v>
       </c>
       <c r="L10" t="n">
-        <v>15.38</v>
+        <v>23.08</v>
       </c>
     </row>
     <row r="11">
@@ -909,19 +909,19 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0.34</v>
+        <v>-0.09</v>
       </c>
       <c r="E11" t="n">
-        <v>1.88</v>
+        <v>2.46</v>
       </c>
       <c r="F11" t="n">
         <v>2.91</v>
       </c>
       <c r="G11" t="n">
-        <v>3.77</v>
+        <v>3.93</v>
       </c>
       <c r="H11" t="n">
-        <v>2.225</v>
+        <v>2.3025</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -955,19 +955,19 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0.52</v>
+        <v>-0.22</v>
       </c>
       <c r="E12" t="n">
-        <v>1.9</v>
+        <v>2.37</v>
       </c>
       <c r="F12" t="n">
-        <v>2.54</v>
+        <v>2.34</v>
       </c>
       <c r="G12" t="n">
-        <v>2.84</v>
+        <v>3.12</v>
       </c>
       <c r="H12" t="n">
-        <v>1.95</v>
+        <v>1.9025</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -975,13 +975,13 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K12" t="n">
         <v>3</v>
       </c>
       <c r="L12" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
     </row>
     <row r="13">
@@ -1001,19 +1001,19 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>0.37</v>
+        <v>2.35</v>
       </c>
       <c r="E13" t="n">
-        <v>0.23</v>
+        <v>3.12</v>
       </c>
       <c r="F13" t="n">
-        <v>0.1</v>
+        <v>-0.12</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.26</v>
+        <v>2.34</v>
       </c>
       <c r="H13" t="n">
-        <v>0.11</v>
+        <v>1.9225</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1021,13 +1021,13 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="K13" t="n">
         <v>14</v>
       </c>
       <c r="L13" t="n">
-        <v>38.46</v>
+        <v>46.15</v>
       </c>
     </row>
     <row r="14">
@@ -1047,19 +1047,19 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>-2.77</v>
+        <v>-0.38</v>
       </c>
       <c r="E14" t="n">
-        <v>1.13</v>
+        <v>2.78</v>
       </c>
       <c r="F14" t="n">
-        <v>4.67</v>
+        <v>2.58</v>
       </c>
       <c r="G14" t="n">
-        <v>-1.49</v>
+        <v>0.49</v>
       </c>
       <c r="H14" t="n">
-        <v>0.385</v>
+        <v>1.3675</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1067,13 +1067,13 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="K14" t="n">
         <v>14</v>
       </c>
       <c r="L14" t="n">
-        <v>53.85</v>
+        <v>38.46</v>
       </c>
     </row>
     <row r="15">
@@ -1093,19 +1093,19 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>-2.1</v>
+        <v>-0.05</v>
       </c>
       <c r="E15" t="n">
-        <v>3.61</v>
+        <v>4.98</v>
       </c>
       <c r="F15" t="n">
-        <v>10.01</v>
+        <v>8.99</v>
       </c>
       <c r="G15" t="n">
-        <v>2.97</v>
+        <v>5.15</v>
       </c>
       <c r="H15" t="n">
-        <v>3.6225</v>
+        <v>4.7675</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1113,13 +1113,13 @@
         </is>
       </c>
       <c r="J15" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K15" t="n">
         <v>14</v>
       </c>
       <c r="L15" t="n">
-        <v>76.92</v>
+        <v>69.23</v>
       </c>
     </row>
     <row r="16">
@@ -1139,19 +1139,19 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>-1.59</v>
+        <v>-0.86</v>
       </c>
       <c r="E16" t="n">
-        <v>1.7</v>
+        <v>2.29</v>
       </c>
       <c r="F16" t="n">
-        <v>4.88</v>
+        <v>4.14</v>
       </c>
       <c r="G16" t="n">
-        <v>-3.65</v>
+        <v>-2.21</v>
       </c>
       <c r="H16" t="n">
-        <v>0.3350000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1159,13 +1159,13 @@
         </is>
       </c>
       <c r="J16" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="K16" t="n">
         <v>14</v>
       </c>
       <c r="L16" t="n">
-        <v>46.15</v>
+        <v>15.38</v>
       </c>
     </row>
     <row r="17">
@@ -1185,19 +1185,19 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>-0.6899999999999999</v>
+        <v>0.66</v>
       </c>
       <c r="E17" t="n">
-        <v>5.77</v>
+        <v>6.09</v>
       </c>
       <c r="F17" t="n">
-        <v>13.4</v>
+        <v>10.91</v>
       </c>
       <c r="G17" t="n">
-        <v>1.78</v>
+        <v>2.94</v>
       </c>
       <c r="H17" t="n">
-        <v>5.065</v>
+        <v>5.15</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -1205,13 +1205,13 @@
         </is>
       </c>
       <c r="J17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K17" t="n">
         <v>14</v>
       </c>
       <c r="L17" t="n">
-        <v>92.31</v>
+        <v>84.62</v>
       </c>
     </row>
     <row r="18">
@@ -1231,19 +1231,19 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>0.44</v>
+        <v>1.52</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.13</v>
+        <v>2.52</v>
       </c>
       <c r="F18" t="n">
-        <v>-2.14</v>
+        <v>-2.27</v>
       </c>
       <c r="G18" t="n">
-        <v>-1.67</v>
+        <v>-0.1</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.875</v>
+        <v>0.4175</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -1277,17 +1277,17 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>-0.41</v>
+        <v>1.69</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.09</v>
+        <v>1.12</v>
       </c>
       <c r="F19" t="n">
-        <v>0.84</v>
+        <v>0.28</v>
       </c>
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="n">
-        <v>-0.22</v>
+        <v>1.03</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -1295,13 +1295,13 @@
         </is>
       </c>
       <c r="J19" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="K19" t="n">
         <v>14</v>
       </c>
       <c r="L19" t="n">
-        <v>23.08</v>
+        <v>30.77</v>
       </c>
     </row>
     <row r="20">
@@ -1321,17 +1321,17 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>2.16</v>
+        <v>5.12</v>
       </c>
       <c r="E20" t="n">
-        <v>1.33</v>
+        <v>6.35</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.17</v>
+        <v>3.56</v>
       </c>
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="n">
-        <v>1.106666666666667</v>
+        <v>5.01</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -1339,13 +1339,13 @@
         </is>
       </c>
       <c r="J20" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="K20" t="n">
         <v>14</v>
       </c>
       <c r="L20" t="n">
-        <v>61.54</v>
+        <v>76.92</v>
       </c>
     </row>
     <row r="21">
@@ -1365,15 +1365,15 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>1.47</v>
+        <v>3.78</v>
       </c>
       <c r="E21" t="n">
-        <v>1.27</v>
+        <v>3.26</v>
       </c>
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr"/>
       <c r="H21" t="n">
-        <v>1.37</v>
+        <v>3.52</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
@@ -1381,13 +1381,13 @@
         </is>
       </c>
       <c r="J21" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K21" t="n">
         <v>14</v>
       </c>
       <c r="L21" t="n">
-        <v>69.23</v>
+        <v>61.54</v>
       </c>
     </row>
   </sheetData>
